--- a/artfynd/A 7218-2022 artfynd.xlsx
+++ b/artfynd/A 7218-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7218-2022 artfynd.xlsx
+++ b/artfynd/A 7218-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99570173</v>
+        <v>99570190</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556669.1838372455</v>
+        <v>556863</v>
       </c>
       <c r="R2" t="n">
-        <v>6290761.349622693</v>
+        <v>6290613</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>99570430</v>
       </c>
       <c r="B3" t="n">
-        <v>83354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,7 +806,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556801.21682797</v>
+        <v>556801</v>
       </c>
       <c r="R3" t="n">
-        <v>6290584.964267599</v>
+        <v>6290585</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +852,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99570190</v>
+        <v>99570179</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,27 +898,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556862.909823182</v>
+        <v>556691</v>
       </c>
       <c r="R4" t="n">
-        <v>6290613.213231118</v>
+        <v>6290750</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,21 +958,11 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>A 7218-2022</t>
@@ -1020,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1038,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99570179</v>
+        <v>99570183</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556690.2101964442</v>
+        <v>556801</v>
       </c>
       <c r="R5" t="n">
-        <v>6290750.121632132</v>
+        <v>6290585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,21 +1064,11 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>A 7218-2022</t>
@@ -1140,7 +1080,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1159,15 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99570183</v>
+        <v>99570173</v>
       </c>
       <c r="B6" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,26 +1109,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1202,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556801.21682797</v>
+        <v>556669</v>
       </c>
       <c r="R6" t="n">
-        <v>6290584.964267599</v>
+        <v>6290761</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,19 +1170,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1282,12 +1207,7 @@
         <v>100532778</v>
       </c>
       <c r="B7" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556847.4280930611</v>
+        <v>556847</v>
       </c>
       <c r="R7" t="n">
-        <v>6290580.108812275</v>
+        <v>6290581</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1365,19 +1285,9 @@
           <t>2022-05-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-05-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 7218-2022 artfynd.xlsx
+++ b/artfynd/A 7218-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99570190</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99570430</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99570179</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99570183</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99570173</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,8 +1347,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100532778</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>